--- a/stock/ostatki_fbo_fbs_2026-10-20.xlsx
+++ b/stock/ostatki_fbo_fbs_2026-10-20.xlsx
@@ -436,7 +436,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>372</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>133</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>240</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>387</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>117</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>123</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>82</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>454</v>
+        <v>386</v>
       </c>
     </row>
     <row r="96">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>316</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>333</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102">
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="116">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>275</v>
+        <v>253</v>
       </c>
     </row>
     <row r="120">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="121">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
     </row>
     <row r="123">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>112</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>282</v>
+        <v>224</v>
       </c>
     </row>
     <row r="133">
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
     </row>
     <row r="134">
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>256</v>
+        <v>196</v>
       </c>
     </row>
     <row r="137">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="145">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="153">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
     </row>
     <row r="172">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>390</v>
+        <v>325</v>
       </c>
     </row>
     <row r="189">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="192">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
     </row>
     <row r="194">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
     </row>
     <row r="198">
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
     </row>
     <row r="199">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>337</v>
+        <v>278</v>
       </c>
     </row>
     <row r="209">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="210">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="211">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="212">
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>114</v>
+        <v>30</v>
       </c>
     </row>
     <row r="220">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
     <row r="221">
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>129</v>
+        <v>64</v>
       </c>
     </row>
     <row r="223">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="228">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
     </row>
     <row r="229">
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>244</v>
+        <v>148</v>
       </c>
     </row>
     <row r="230">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="231">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>227</v>
+        <v>148</v>
       </c>
     </row>
     <row r="232">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>156</v>
+        <v>105</v>
       </c>
     </row>
     <row r="233">
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>295</v>
+        <v>213</v>
       </c>
     </row>
     <row r="234">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>119</v>
+        <v>77</v>
       </c>
     </row>
     <row r="235">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>293</v>
+        <v>240</v>
       </c>
     </row>
     <row r="236">
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="237">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>573</v>
+        <v>528</v>
       </c>
     </row>
     <row r="238">
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="239">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>202</v>
+        <v>172</v>
       </c>
     </row>
     <row r="241">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="243">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="244">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
     </row>
     <row r="245">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="247">
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="248">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="249">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="251">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>138</v>
+        <v>81</v>
       </c>
     </row>
     <row r="252">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>160</v>
+        <v>103</v>
       </c>
     </row>
     <row r="253">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="254">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>449</v>
+        <v>403</v>
       </c>
     </row>
     <row r="256">
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
     </row>
     <row r="257">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>338</v>
+        <v>306</v>
       </c>
     </row>
     <row r="259">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>141</v>
+        <v>98</v>
       </c>
     </row>
     <row r="261">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="263">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="264">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>107</v>
+        <v>26</v>
       </c>
     </row>
     <row r="269">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="270">
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275">
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276">
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>524</v>
+        <v>460</v>
       </c>
     </row>
     <row r="280">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>452</v>
+        <v>428</v>
       </c>
     </row>
     <row r="281">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
     </row>
     <row r="282">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
     </row>
     <row r="283">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>336</v>
+        <v>223</v>
       </c>
     </row>
     <row r="284">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>403</v>
+        <v>220</v>
       </c>
     </row>
     <row r="285">
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>298</v>
+        <v>205</v>
       </c>
     </row>
     <row r="288">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="289">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>196</v>
+        <v>50</v>
       </c>
     </row>
     <row r="290">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>180</v>
+        <v>146</v>
       </c>
     </row>
     <row r="291">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>260</v>
+        <v>229</v>
       </c>
     </row>
     <row r="292">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>274</v>
+        <v>161</v>
       </c>
     </row>
     <row r="293">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="294">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="295">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>271</v>
+        <v>147</v>
       </c>
     </row>
     <row r="296">
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>651</v>
+        <v>507</v>
       </c>
     </row>
     <row r="300">
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="301">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="302">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="303">
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="304">
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="306">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="307">
@@ -3508,7 +3508,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="308">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="309">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="310">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="311">
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="312">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>204</v>
+        <v>169</v>
       </c>
     </row>
     <row r="313">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="314">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>451</v>
+        <v>353</v>
       </c>
     </row>
     <row r="316">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="317">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
     </row>
     <row r="318">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="321">
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>282</v>
+        <v>249</v>
       </c>
     </row>
     <row r="322">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="323">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="336">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="344">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="350">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="351">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
     </row>
     <row r="353">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="354">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="355">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="356">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="357">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="358">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
     </row>
     <row r="359">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="362">
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="363">
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="364">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="367">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="368">
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="369">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="372">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="373">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>511</v>
+        <v>484</v>
       </c>
     </row>
     <row r="377">
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="378">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="379">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="380">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="385">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>208</v>
+        <v>130</v>
       </c>
     </row>
     <row r="386">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="387">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="388">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="389">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="390">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>645</v>
+        <v>614</v>
       </c>
     </row>
     <row r="391">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="392">
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
     </row>
     <row r="394">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>333</v>
+        <v>292</v>
       </c>
     </row>
     <row r="395">
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="396">
@@ -4398,7 +4398,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="397">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="398">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="399">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="401">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>185</v>
+        <v>73</v>
       </c>
     </row>
     <row r="405">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="406">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>151</v>
+        <v>62</v>
       </c>
     </row>
     <row r="407">
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>259</v>
+        <v>167</v>
       </c>
     </row>
     <row r="408">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
     </row>
     <row r="409">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>145</v>
+        <v>52</v>
       </c>
     </row>
     <row r="410">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
     </row>
     <row r="411">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>140</v>
+        <v>79</v>
       </c>
     </row>
     <row r="412">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>181</v>
+        <v>98</v>
       </c>
     </row>
     <row r="413">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>186</v>
+        <v>113</v>
       </c>
     </row>
     <row r="414">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>185</v>
+        <v>98</v>
       </c>
     </row>
     <row r="415">
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>154</v>
+        <v>97</v>
       </c>
     </row>
     <row r="416">
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
     </row>
     <row r="417">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>249</v>
+        <v>164</v>
       </c>
     </row>
     <row r="419">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>114</v>
+        <v>86</v>
       </c>
     </row>
     <row r="420">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>192</v>
+        <v>118</v>
       </c>
     </row>
     <row r="421">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>107</v>
+        <v>40</v>
       </c>
     </row>
     <row r="422">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="426">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="427">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="428">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="429">
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="430">
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="431">
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
     </row>
     <row r="432">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="433">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="435">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="436">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="438">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
     </row>
     <row r="439">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="440">
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>504</v>
+        <v>420</v>
       </c>
     </row>
     <row r="442">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>466</v>
+        <v>455</v>
       </c>
     </row>
     <row r="443">
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>371</v>
+        <v>257</v>
       </c>
     </row>
     <row r="444">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="446">
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="447">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="448">
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="449">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>617</v>
+        <v>595</v>
       </c>
     </row>
     <row r="455">
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>495</v>
+        <v>441</v>
       </c>
     </row>
     <row r="456">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="457">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="458">
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="459">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="460">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="461">
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
     </row>
     <row r="462">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="463">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="464">
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="465">
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="466">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="468">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="470">
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="472">
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="473">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
     </row>
     <row r="474">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -5228,9 +5228,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FBO (склады РФ)</t>
+          <t>FBO (Склад WB РФ)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>326</v>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
         <v>86</v>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
         <v>184</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="C34" t="n">
         <v>305</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>81</v>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="C41" t="n">
         <v>27</v>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="C43" t="n">
         <v>28</v>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
         <v>7</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C45" t="n">
         <v>10</v>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C46" t="n">
         <v>14</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
         <v>23</v>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C49" t="n">
         <v>70</v>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C50" t="n">
         <v>15</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C51" t="n">
         <v>14</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
         <v>36</v>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C53" t="n">
         <v>8</v>
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C54" t="n">
         <v>54</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C62" t="n">
         <v>74</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
         <v>59</v>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -6826,7 +6826,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
         <v>385</v>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C97" t="n">
         <v>278</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>24</v>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
         <v>270</v>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
         <v>96</v>
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C102" t="n">
         <v>79</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C111" t="n">
         <v>14</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C113" t="n">
         <v>17</v>
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C114" t="n">
         <v>99</v>
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C115" t="n">
         <v>152</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C119" t="n">
         <v>250</v>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C120" t="n">
         <v>224</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C122" t="n">
         <v>81</v>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C123" t="n">
         <v>56</v>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C132" t="n">
         <v>222</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C133" t="n">
         <v>83</v>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C136" t="n">
         <v>195</v>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
         <v>13</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C142" t="n">
         <v>29</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C144" t="n">
         <v>88</v>
@@ -7693,7 +7693,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
         <v>24</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
         <v>21</v>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C150" t="n">
         <v>20</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
         <v>91</v>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -8033,7 +8033,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C188" t="n">
         <v>318</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="C190" t="n">
         <v>3</v>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="C191" t="n">
         <v>36</v>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C193" t="n">
         <v>36</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="C197" t="n">
         <v>23</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="C198" t="n">
         <v>33</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="C203" t="n">
         <v>41</v>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="C208" t="n">
         <v>261</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C209" t="n">
         <v>71</v>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C210" t="n">
         <v>31</v>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C211" t="n">
         <v>101</v>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="C212" t="n">
         <v>22</v>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="C219" t="n">
         <v>12</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="C222" t="n">
         <v>31</v>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -9087,7 +9087,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C227" t="n">
         <v>126</v>
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="C228" t="n">
         <v>37</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="C229" t="n">
         <v>138</v>
@@ -9138,7 +9138,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
         <v>26</v>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="C231" t="n">
         <v>146</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C232" t="n">
         <v>105</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="C233" t="n">
         <v>208</v>
@@ -9206,7 +9206,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C234" t="n">
         <v>75</v>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C235" t="n">
         <v>240</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C236" t="n">
         <v>320</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C237" t="n">
         <v>525</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C238" t="n">
         <v>85</v>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C239" t="n">
         <v>20</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C240" t="n">
         <v>167</v>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="C242" t="n">
         <v>11</v>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C243" t="n">
         <v>159</v>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C244" t="n">
         <v>293</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C246" t="n">
         <v>145</v>
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C247" t="n">
         <v>47</v>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="C248" t="n">
         <v>117</v>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C250" t="n">
         <v>83</v>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="C251" t="n">
         <v>81</v>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="C252" t="n">
         <v>102</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C253" t="n">
         <v>43</v>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="C255" t="n">
         <v>402</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
         <v>168</v>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C258" t="n">
         <v>303</v>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C260" t="n">
         <v>97</v>
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
         <v>22</v>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C263" t="n">
         <v>84</v>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="C279" t="n">
         <v>424</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C280" t="n">
         <v>425</v>
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C281" t="n">
         <v>149</v>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C282" t="n">
         <v>47</v>
@@ -10039,7 +10039,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="C283" t="n">
         <v>201</v>
@@ -10056,7 +10056,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>188</v>
+        <v>5</v>
       </c>
       <c r="C284" t="n">
         <v>215</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C285" t="n">
         <v>1</v>
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C287" t="n">
         <v>192</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C288" t="n">
         <v>32</v>
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C290" t="n">
         <v>111</v>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C291" t="n">
         <v>221</v>
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="C292" t="n">
         <v>155</v>
@@ -10209,7 +10209,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C293" t="n">
         <v>29</v>
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="C295" t="n">
         <v>139</v>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C296" t="n">
         <v>1</v>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="C299" t="n">
         <v>502</v>
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C300" t="n">
         <v>141</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C301" t="n">
         <v>65</v>
@@ -10362,7 +10362,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C302" t="n">
         <v>71</v>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C303" t="n">
         <v>157</v>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C305" t="n">
         <v>101</v>
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C306" t="n">
         <v>54</v>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C307" t="n">
         <v>0</v>
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C309" t="n">
         <v>37</v>
@@ -10498,7 +10498,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C310" t="n">
         <v>130</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C311" t="n">
         <v>25</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C312" t="n">
         <v>119</v>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C313" t="n">
         <v>61</v>
@@ -10566,7 +10566,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C314" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="C315" t="n">
         <v>308</v>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C316" t="n">
         <v>35</v>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C317" t="n">
         <v>236</v>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C319" t="n">
         <v>0</v>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C320" t="n">
         <v>175</v>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C321" t="n">
         <v>245</v>
@@ -10702,7 +10702,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C322" t="n">
         <v>6</v>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C335" t="n">
         <v>6</v>
@@ -11059,7 +11059,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C343" t="n">
         <v>31</v>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C347" t="n">
         <v>0</v>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C349" t="n">
         <v>24</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C350" t="n">
         <v>29</v>
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C352" t="n">
         <v>89</v>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C353" t="n">
         <v>0</v>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C354" t="n">
         <v>0</v>
@@ -11263,7 +11263,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C355" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C356" t="n">
         <v>105</v>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C357" t="n">
         <v>162</v>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C358" t="n">
         <v>167</v>
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C359" t="n">
         <v>0</v>
@@ -11348,7 +11348,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C360" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C361" t="n">
         <v>338</v>
@@ -11382,7 +11382,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C362" t="n">
         <v>76</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C363" t="n">
         <v>76</v>
@@ -11416,7 +11416,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C364" t="n">
         <v>0</v>
@@ -11433,7 +11433,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C365" t="n">
         <v>0</v>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C366" t="n">
         <v>191</v>
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C367" t="n">
         <v>174</v>
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C368" t="n">
         <v>179</v>
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C369" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C370" t="n">
         <v>0</v>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C371" t="n">
         <v>86</v>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C372" t="n">
         <v>0</v>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C373" t="n">
         <v>0</v>
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C374" t="n">
         <v>0</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C375" t="n">
         <v>0</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C376" t="n">
         <v>483</v>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C377" t="n">
         <v>196</v>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C378" t="n">
         <v>43</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C379" t="n">
         <v>217</v>
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C384" t="n">
         <v>41</v>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="C385" t="n">
         <v>115</v>
@@ -11790,7 +11790,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C386" t="n">
         <v>70</v>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C387" t="n">
         <v>145</v>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C388" t="n">
         <v>176</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C389" t="n">
         <v>16</v>
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C390" t="n">
         <v>562</v>
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C391" t="n">
         <v>36</v>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C393" t="n">
         <v>83</v>
@@ -11926,7 +11926,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="C394" t="n">
         <v>201</v>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C395" t="n">
         <v>103</v>
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C396" t="n">
         <v>76</v>
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C397" t="n">
         <v>2</v>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C398" t="n">
         <v>86</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C400" t="n">
         <v>57</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C401" t="n">
         <v>0</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C402" t="n">
         <v>0</v>
@@ -12079,7 +12079,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C403" t="n">
         <v>0</v>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="C404" t="n">
         <v>42</v>
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="C405" t="n">
         <v>80</v>
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="C406" t="n">
         <v>35</v>
@@ -12147,7 +12147,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="C407" t="n">
         <v>124</v>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="C408" t="n">
         <v>20</v>
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="C409" t="n">
         <v>28</v>
@@ -12198,7 +12198,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C410" t="n">
         <v>25</v>
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="C411" t="n">
         <v>45</v>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="C412" t="n">
         <v>93</v>
@@ -12249,7 +12249,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C413" t="n">
         <v>74</v>
@@ -12266,7 +12266,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="C414" t="n">
         <v>83</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="C415" t="n">
         <v>42</v>
@@ -12300,7 +12300,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C416" t="n">
         <v>18</v>
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="C418" t="n">
         <v>101</v>
@@ -12351,7 +12351,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C419" t="n">
         <v>77</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="C420" t="n">
         <v>61</v>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="C421" t="n">
         <v>29</v>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C425" t="n">
         <v>69</v>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C426" t="n">
         <v>78</v>
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C427" t="n">
         <v>183</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C428" t="n">
         <v>26</v>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C429" t="n">
         <v>47</v>
@@ -12538,7 +12538,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C430" t="n">
         <v>90</v>
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C431" t="n">
         <v>89</v>
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C432" t="n">
         <v>17</v>
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C433" t="n">
         <v>0</v>
@@ -12606,7 +12606,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C434" t="n">
         <v>0</v>
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C435" t="n">
         <v>33</v>
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C437" t="n">
         <v>0</v>
@@ -12674,7 +12674,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C438" t="n">
         <v>69</v>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C439" t="n">
         <v>0</v>
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C440" t="n">
         <v>0</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="C441" t="n">
         <v>418</v>
@@ -12742,7 +12742,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C442" t="n">
         <v>455</v>
@@ -12759,7 +12759,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="C443" t="n">
         <v>255</v>
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C445" t="n">
         <v>390</v>
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C446" t="n">
         <v>34</v>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C447" t="n">
         <v>100</v>
@@ -12844,7 +12844,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C448" t="n">
         <v>182</v>
@@ -12861,7 +12861,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C449" t="n">
         <v>0</v>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C450" t="n">
         <v>0</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C451" t="n">
         <v>0</v>
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C452" t="n">
         <v>0</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C453" t="n">
         <v>0</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C454" t="n">
         <v>546</v>
@@ -12963,7 +12963,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="C455" t="n">
         <v>249</v>
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C456" t="n">
         <v>136</v>
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C457" t="n">
         <v>141</v>
@@ -13014,7 +13014,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C458" t="n">
         <v>0</v>
@@ -13031,7 +13031,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C459" t="n">
         <v>0</v>
@@ -13048,7 +13048,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C460" t="n">
         <v>0</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C461" t="n">
         <v>0</v>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C462" t="n">
         <v>0</v>
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C463" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C464" t="n">
         <v>0</v>
@@ -13133,7 +13133,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="C465" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="C466" t="n">
         <v>0</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C467" t="n">
         <v>0</v>
@@ -13184,7 +13184,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C468" t="n">
         <v>0</v>
@@ -13201,7 +13201,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C469" t="n">
         <v>0</v>
@@ -13218,7 +13218,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C470" t="n">
         <v>0</v>
@@ -13235,7 +13235,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C471" t="n">
         <v>46</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C472" t="n">
         <v>17</v>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C473" t="n">
         <v>0</v>
@@ -13320,7 +13320,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C476" t="n">
         <v>0</v>
